--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487847_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487847_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>H. ARBOSA ROLDAN</t>
+          <t>J. QUEREJETA MARTINEZ DE ARENAZA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8453</v>
+        <v>5.285</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7685</v>
+        <v>3.1442</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0769</v>
+        <v>2.1409</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.1154</v>
+        <v>1.0771</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9616</v>
+        <v>1.5776</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.077</v>
+        <v>-0.5004999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5829</v>
+        <v>1.2406</v>
       </c>
       <c r="K2" t="n">
-        <v>1.7373</v>
+        <v>1.2104</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.1544</v>
+        <v>0.0302</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6982</v>
+        <v>-0.1635</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2243</v>
+        <v>0.3672</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.9225</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>2.0812</v>
+        <v>2.2893</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0812</v>
+        <v>2.2893</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1906</v>
+        <v>-0.5226</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2668</v>
+        <v>-0.5376</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9239000000000001</v>
+        <v>0.0151</v>
       </c>
       <c r="V2" t="n">
-        <v>2.6889</v>
+        <v>2.4412</v>
       </c>
       <c r="W2" t="n">
-        <v>2.9188</v>
+        <v>2.4412</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. QUEREJETA MARTINEZ DE ARENAZA</t>
+          <t>H. ARBOSA ROLDAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5139</v>
+        <v>5.1339</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5198</v>
+        <v>3.3212</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9941</v>
+        <v>1.8126</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0771</v>
+        <v>-0.1154</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5776</v>
+        <v>1.9616</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5004999999999999</v>
+        <v>-2.077</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2406</v>
+        <v>0.5829</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2104</v>
+        <v>1.7373</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0302</v>
+        <v>-1.1544</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1635</v>
+        <v>-0.6982</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3672</v>
+        <v>0.2243</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5306999999999999</v>
+        <v>-0.9225</v>
       </c>
       <c r="P3" t="n">
-        <v>2.2893</v>
+        <v>2.0812</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2893</v>
+        <v>2.0812</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.2937</v>
+        <v>0.4792</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.162</v>
+        <v>-0.1804</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1317</v>
+        <v>0.6597</v>
       </c>
       <c r="V3" t="n">
-        <v>2.4412</v>
+        <v>2.6889</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4412</v>
+        <v>2.9188</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.1014</v>
+        <v>3.3732</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5909</v>
+        <v>-0.9962</v>
       </c>
       <c r="F4" t="n">
-        <v>4.6923</v>
+        <v>4.3694</v>
       </c>
       <c r="G4" t="n">
         <v>2.6579</v>
@@ -766,13 +766,13 @@
         <v>1.8731</v>
       </c>
       <c r="S4" t="n">
-        <v>0.841</v>
+        <v>0.1127</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1239</v>
+        <v>-0.2814</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7171</v>
+        <v>0.3941</v>
       </c>
       <c r="V4" t="n">
         <v>-0.23</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. JACOBS</t>
+          <t>I. ROYO ARGOTE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1183</v>
+        <v>1.447</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4374</v>
+        <v>-0.4845</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5556</v>
+        <v>1.9315</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1985</v>
+        <v>-0.5065</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7119</v>
+        <v>1.0235</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4866</v>
+        <v>-1.53</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6065</v>
+        <v>-1.8086</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1934</v>
+        <v>-0.2051</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4131</v>
+        <v>-1.6035</v>
       </c>
       <c r="M5" t="n">
-        <v>1.592</v>
+        <v>1.3021</v>
       </c>
       <c r="N5" t="n">
-        <v>1.5185</v>
+        <v>1.2286</v>
       </c>
       <c r="O5" t="n">
         <v>0.0735</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2081</v>
+        <v>1.2487</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>1.2487</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2446</v>
+        <v>-0.4627</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0033</v>
+        <v>-0.6572</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2413</v>
+        <v>0.1945</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0437</v>
+        <v>1.1675</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.9813</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0437</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. ROYO ARGOTE</t>
+          <t>C. JACOBS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0016</v>
+        <v>1.0074</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8712</v>
+        <v>-0.3721</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8728</v>
+        <v>1.3795</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5065</v>
+        <v>2.1985</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0235</v>
+        <v>1.7119</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.53</v>
+        <v>0.4866</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.8086</v>
+        <v>0.6065</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2051</v>
+        <v>0.1934</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.6035</v>
+        <v>0.4131</v>
       </c>
       <c r="M6" t="n">
-        <v>1.3021</v>
+        <v>1.592</v>
       </c>
       <c r="N6" t="n">
-        <v>1.2286</v>
+        <v>1.5185</v>
       </c>
       <c r="O6" t="n">
         <v>0.0735</v>
       </c>
       <c r="P6" t="n">
-        <v>1.2487</v>
+        <v>0.2081</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R6" t="n">
         <v>1.2487</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9081</v>
+        <v>-0.3555</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0439</v>
+        <v>0.0619</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1358</v>
+        <v>-0.4175</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1675</v>
+        <v>-1.0437</v>
       </c>
       <c r="W6" t="n">
-        <v>1.9813</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8137</v>
+        <v>-1.0437</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0124</v>
+        <v>0.8944</v>
       </c>
       <c r="E7" t="n">
-        <v>2.6567</v>
+        <v>3.2158</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.6444</v>
+        <v>-2.3214</v>
       </c>
       <c r="G7" t="n">
         <v>0.7853</v>
@@ -1000,13 +1000,13 @@
         <v>0.8325</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9186</v>
+        <v>-0.0365</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.901</v>
+        <v>-0.3419</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0176</v>
+        <v>0.3054</v>
       </c>
       <c r="V7" t="n">
         <v>0.3538</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. DIENE</t>
+          <t>O. OKAFOR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2766</v>
+        <v>-0.3674</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0586</v>
+        <v>0.3804</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.218</v>
+        <v>-0.7478</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5754</v>
+        <v>-0.0503</v>
       </c>
       <c r="H8" t="n">
-        <v>1.6056</v>
+        <v>-0.3752</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0302</v>
+        <v>0.3249</v>
       </c>
       <c r="J8" t="n">
-        <v>2.5839</v>
+        <v>-0.042</v>
       </c>
       <c r="K8" t="n">
-        <v>1.7609</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>0.823</v>
+        <v>0.0392</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0085</v>
+        <v>-0.0083</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1553</v>
+        <v>-0.294</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8532</v>
+        <v>0.2857</v>
       </c>
       <c r="P8" t="n">
+        <v>0.6244</v>
+      </c>
+      <c r="Q8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-1.0406</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.0406</v>
+        <v>0.6244</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2531</v>
+        <v>-0.0039</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1866</v>
+        <v>0.1924</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4398</v>
+        <v>-0.1964</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.1051</v>
+        <v>-0.9376</v>
       </c>
       <c r="W8" t="n">
-        <v>-1.4152</v>
+        <v>0.23</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6899</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. OKAFOR</t>
+          <t>P. DIENE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3968</v>
+        <v>-0.4</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3804</v>
+        <v>-0.0352</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7772</v>
+        <v>-0.3648</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0503</v>
+        <v>1.5754</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3752</v>
+        <v>1.6056</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3249</v>
+        <v>-0.0302</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.042</v>
+        <v>2.5839</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.08119999999999999</v>
+        <v>1.7609</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0392</v>
+        <v>0.823</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0083</v>
+        <v>-1.0085</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.294</v>
+        <v>-0.1553</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2857</v>
+        <v>-0.8532</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6244</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6244</v>
+        <v>1.0406</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0333</v>
+        <v>0.1297</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1924</v>
+        <v>-0.1633</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2257</v>
+        <v>0.293</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9376</v>
+        <v>-2.1051</v>
       </c>
       <c r="W9" t="n">
-        <v>0.23</v>
+        <v>-1.4152</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1675</v>
+        <v>-0.6899</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. A NONGO BERTHOLD</t>
+          <t>M. DE PABLO DEL CASTILLO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5317</v>
+        <v>-1.1958</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7873</v>
+        <v>-0.6883</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7443</v>
+        <v>-0.5075</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4568</v>
+        <v>4.1236</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4201</v>
+        <v>0.9747</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0367</v>
+        <v>3.1489</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0044</v>
+        <v>3.6217</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0044</v>
+        <v>0.6524</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.9693</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4612</v>
+        <v>0.5019</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4245</v>
+        <v>0.3223</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0367</v>
+        <v>0.1796</v>
       </c>
       <c r="P10" t="n">
+        <v>-3.538</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-4.1624</v>
+      </c>
+      <c r="R10" t="n">
         <v>0.6244</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-1.0406</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.6649</v>
-      </c>
       <c r="S10" t="n">
-        <v>0.306</v>
+        <v>-0.2601</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2577</v>
+        <v>-0.3776</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0483</v>
+        <v>0.1175</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.9188</v>
+        <v>-1.5213</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.9188</v>
+        <v>-1.7513</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. DE PABLO DEL CASTILLO</t>
+          <t>E. A NONGO BERTHOLD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9958</v>
+        <v>-1.9999</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2241</v>
+        <v>-1.1088</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7718</v>
+        <v>-0.8911</v>
       </c>
       <c r="G11" t="n">
-        <v>4.1236</v>
+        <v>0.4568</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9747</v>
+        <v>0.4201</v>
       </c>
       <c r="I11" t="n">
-        <v>3.1489</v>
+        <v>0.0367</v>
       </c>
       <c r="J11" t="n">
-        <v>3.6217</v>
+        <v>-0.0044</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6524</v>
+        <v>-0.0044</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9693</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5019</v>
+        <v>0.4612</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3223</v>
+        <v>0.4245</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1796</v>
+        <v>0.0367</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.538</v>
+        <v>0.6244</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.1624</v>
+        <v>-1.0406</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6244</v>
+        <v>1.6649</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0602</v>
+        <v>-0.1623</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9134</v>
+        <v>-0.0638</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1468</v>
+        <v>-0.0985</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.5213</v>
+        <v>-2.9188</v>
       </c>
       <c r="W11" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.7513</v>
+        <v>-2.9188</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.317</v>
+        <v>-2.1241</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9381</v>
+        <v>-0.98</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3789</v>
+        <v>-1.1441</v>
       </c>
       <c r="G12" t="n">
         <v>-0.8742</v>
@@ -1390,13 +1390,13 @@
         <v>1.0406</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2753</v>
+        <v>-0.0824</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0743</v>
+        <v>0.0324</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3497</v>
+        <v>-0.1148</v>
       </c>
       <c r="V12" t="n">
         <v>-1.1675</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.075</v>
+        <v>11.0537</v>
       </c>
       <c r="E13" t="n">
-        <v>4.4178</v>
+        <v>5.3965</v>
       </c>
       <c r="F13" t="n">
-        <v>5.6571</v>
+        <v>5.6572</v>
       </c>
       <c r="G13" t="n">
         <v>11.3282</v>
@@ -1444,7 +1444,7 @@
         <v>10.1055</v>
       </c>
       <c r="K13" t="n">
-        <v>6.5744</v>
+        <v>6.574400000000001</v>
       </c>
       <c r="L13" t="n">
         <v>3.531</v>
@@ -1453,7 +1453,7 @@
         <v>1.222900000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>3.6926</v>
+        <v>3.692599999999999</v>
       </c>
       <c r="O13" t="n">
         <v>-2.469799999999999</v>
@@ -1468,19 +1468,19 @@
         <v>14.5684</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.1431</v>
+        <v>-1.1644</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.295100000000001</v>
+        <v>-2.3165</v>
       </c>
       <c r="U13" t="n">
         <v>1.1521</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.2726</v>
+        <v>-3.272600000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>8.013599999999999</v>
+        <v>8.0136</v>
       </c>
       <c r="X13" t="n">
         <v>-11.2861</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.04</v>
+        <v>5.1249</v>
       </c>
       <c r="E14" t="n">
-        <v>7.9276</v>
+        <v>6.4274</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8875</v>
+        <v>-1.3025</v>
       </c>
       <c r="G14" t="n">
         <v>3.0761</v>
@@ -1546,13 +1546,13 @@
         <v>1.8731</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2314</v>
+        <v>1.3162</v>
       </c>
       <c r="T14" t="n">
-        <v>2.006</v>
+        <v>0.5058</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2253</v>
+        <v>0.8104</v>
       </c>
       <c r="V14" t="n">
         <v>1.9813</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3545</v>
+        <v>3.9054</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0768</v>
+        <v>3.7198</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2777</v>
+        <v>0.1857</v>
       </c>
       <c r="G15" t="n">
         <v>1.4429</v>
@@ -1624,13 +1624,13 @@
         <v>1.0406</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1572</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7334000000000001</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8905999999999999</v>
+        <v>0.7986</v>
       </c>
       <c r="V15" t="n">
         <v>2.795</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. GONZALEZ CORDERO</t>
+          <t>J. LLAMAS PRADO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.0197</v>
+        <v>-0.7834</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8084</v>
+        <v>-3.214</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8281</v>
+        <v>2.4306</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1347</v>
+        <v>0.4142</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4115</v>
+        <v>-2.0384</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2768</v>
+        <v>2.4525</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7308</v>
+        <v>0.4634</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6524</v>
+        <v>-1.8789</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0784</v>
+        <v>2.3423</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.596</v>
+        <v>-0.0492</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2409</v>
+        <v>-0.1595</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3551</v>
+        <v>0.1102</v>
       </c>
       <c r="P16" t="n">
+        <v>-1.0406</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-3.1218</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.0812</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.078</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.3987</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-0.4776</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-0.4776</v>
+      </c>
+      <c r="X16" t="n">
         <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.0776</v>
-      </c>
-      <c r="U16" t="n">
-        <v>-0.0646</v>
-      </c>
-      <c r="V16" t="n">
-        <v>-1.1675</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>-1.1675</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. VAN DER HEIJDEN</t>
+          <t>A. GONZALEZ CORDERO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.4714</v>
+        <v>-0.7951</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1968</v>
+        <v>0.9156</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2745</v>
+        <v>-1.7107</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.5667</v>
+        <v>0.1347</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.2369</v>
+        <v>0.4115</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3298</v>
+        <v>-0.2768</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0581</v>
+        <v>0.7308</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6081</v>
+        <v>0.6524</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6662</v>
+        <v>0.0784</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6248</v>
+        <v>-0.596</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6288</v>
+        <v>-0.2409</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.996</v>
+        <v>-0.3551</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6244</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4162</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2421</v>
+        <v>0.2376</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4443</v>
+        <v>0.1848</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6864</v>
+        <v>0.0529</v>
       </c>
       <c r="V17" t="n">
-        <v>0.4776</v>
+        <v>-1.1675</v>
       </c>
       <c r="W17" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.2477</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. LLAMAS PRADO</t>
+          <t>A. DOMINGUEZ ESPELT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6573</v>
+        <v>-1.1412</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.857</v>
+        <v>-0.6283</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1997</v>
+        <v>-0.5129</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4142</v>
+        <v>-0.7506</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.0384</v>
+        <v>1.5288</v>
       </c>
       <c r="I18" t="n">
-        <v>2.4525</v>
+        <v>-2.2795</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4634</v>
+        <v>0.1027</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.8789</v>
+        <v>2.2066</v>
       </c>
       <c r="L18" t="n">
-        <v>2.3423</v>
+        <v>-2.1039</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0492</v>
+        <v>-0.8532999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1595</v>
+        <v>-0.6778</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1102</v>
+        <v>-0.1755</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.0406</v>
+        <v>0.8325</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0812</v>
+        <v>0.8325</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5532</v>
+        <v>0.0683</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.721</v>
+        <v>-0.2533</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1677</v>
+        <v>0.3217</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.4776</v>
+        <v>-1.2914</v>
       </c>
       <c r="W18" t="n">
         <v>-0.4776</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. DOMINGUEZ ESPELT</t>
+          <t>E. VAN DER HEIJDEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7817</v>
+        <v>-1.5697</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9497</v>
+        <v>-1.0897</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8319</v>
+        <v>-0.4801</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7506</v>
+        <v>-1.5667</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5288</v>
+        <v>-1.2369</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.2795</v>
+        <v>-0.3298</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1027</v>
+        <v>0.0581</v>
       </c>
       <c r="K19" t="n">
-        <v>2.2066</v>
+        <v>-0.6081</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.1039</v>
+        <v>0.6662</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8532999999999999</v>
+        <v>-1.6248</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6778</v>
+        <v>-0.6288</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1755</v>
+        <v>-0.996</v>
       </c>
       <c r="P19" t="n">
-        <v>0.8325</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8325</v>
+        <v>0.4162</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5722</v>
+        <v>0.1437</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5748</v>
+        <v>-0.3372</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0026</v>
+        <v>0.4809</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2914</v>
+        <v>0.4776</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.4776</v>
+        <v>0.23</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.8137</v>
+        <v>0.2477</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0254</v>
+        <v>-1.7715</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9679</v>
+        <v>-1.8607</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0576</v>
+        <v>0.0892</v>
       </c>
       <c r="G20" t="n">
         <v>-2.291</v>
@@ -2014,13 +2014,13 @@
         <v>0.4162</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1507</v>
+        <v>0.1032</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.171</v>
+        <v>-0.0638</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0202</v>
+        <v>0.167</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. HAYMAN</t>
+          <t>D. CEBOLLA PORCAR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6825</v>
+        <v>-2.6557</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5609</v>
+        <v>-2.4882</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1216</v>
+        <v>-0.1675</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.9551</v>
+        <v>-3.0278</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.2196</v>
+        <v>-2.062</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2645</v>
+        <v>-0.9658</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2772</v>
+        <v>-2.2561</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.3948</v>
+        <v>-1.5719</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1176</v>
+        <v>-0.6842</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8248</v>
+        <v>-0.4901</v>
       </c>
       <c r="O21" t="n">
-        <v>0.147</v>
+        <v>-0.2817</v>
       </c>
       <c r="P21" t="n">
+        <v>-0.2081</v>
+      </c>
+      <c r="Q21" t="n">
         <v>-1.0406</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-2.0812</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.0406</v>
+        <v>0.8325</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1644</v>
+        <v>-0.1274</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.37</v>
+        <v>-0.359</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2056</v>
+        <v>0.2317</v>
       </c>
       <c r="V21" t="n">
-        <v>0.4776</v>
+        <v>0.7076</v>
       </c>
       <c r="W21" t="n">
         <v>1.1675</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6899</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. LLAMAS MARTINEZ</t>
+          <t>D. HAYMAN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.892</v>
+        <v>-2.6913</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8948</v>
+        <v>-2.7752</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9972</v>
+        <v>0.0839</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.5984</v>
+        <v>-1.9551</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2684</v>
+        <v>-2.2196</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.3301</v>
+        <v>0.2645</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.3042</v>
+        <v>-1.2772</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1727</v>
+        <v>-1.3948</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.4769</v>
+        <v>0.1176</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.2942</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4411</v>
+        <v>-0.8248</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8532</v>
+        <v>0.147</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.4162</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6244</v>
+        <v>1.0406</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1226</v>
+        <v>-0.1732</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2824</v>
+        <v>-0.5843</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1598</v>
+        <v>0.4111</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.4776</v>
       </c>
       <c r="W22" t="n">
         <v>1.1675</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.1675</v>
+        <v>-0.6899</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. CEBOLLA PORCAR</t>
+          <t>R. LLAMAS MARTINEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1533</v>
+        <v>-2.9238</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8096</v>
+        <v>-1.2163</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3437</v>
+        <v>-1.7075</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.0278</v>
+        <v>-2.5984</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.062</v>
+        <v>-0.2684</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9658</v>
+        <v>-2.3301</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.2561</v>
+        <v>-1.3042</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.5719</v>
+        <v>0.1727</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6842</v>
+        <v>-1.4769</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7717000000000001</v>
+        <v>-1.2942</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4901</v>
+        <v>-0.4411</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2817</v>
+        <v>-0.8532</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.2081</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q23" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R23" t="n">
-        <v>0.8325</v>
+        <v>0.6244</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.625</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6805</v>
+        <v>-0.039</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0555</v>
+        <v>0.1299</v>
       </c>
       <c r="V23" t="n">
-        <v>0.7076</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>1.1675</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.4599</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.7862</v>
+        <v>-4.0592</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.2332</v>
+        <v>-3.4476</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5528999999999999</v>
+        <v>-0.6116</v>
       </c>
       <c r="G24" t="n">
         <v>-4.2067</v>
@@ -2326,13 +2326,13 @@
         <v>1.2487</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4423</v>
+        <v>0.1693</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1767</v>
+        <v>-0.0376</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2656</v>
+        <v>0.2069</v>
       </c>
       <c r="V24" t="n">
         <v>-0.23</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-10.075</v>
+        <v>-9.360599999999998</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.6571</v>
+        <v>-5.6572</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.4176</v>
+        <v>-3.7034</v>
       </c>
       <c r="G25" t="n">
         <v>-11.3284</v>
@@ -2380,7 +2380,7 @@
         <v>-1.222899999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.6926</v>
+        <v>-3.692600000000001</v>
       </c>
       <c r="L25" t="n">
         <v>2.4697</v>
@@ -2404,16 +2404,16 @@
         <v>10.406</v>
       </c>
       <c r="S25" t="n">
-        <v>2.1431</v>
+        <v>2.8573</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.1523</v>
+        <v>-1.152</v>
       </c>
       <c r="U25" t="n">
-        <v>3.2951</v>
+        <v>4.0098</v>
       </c>
       <c r="V25" t="n">
-        <v>3.2726</v>
+        <v>3.272599999999999</v>
       </c>
       <c r="W25" t="n">
         <v>11.2861</v>
